--- a/data/trans_dic/P55$privada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,26</t>
+          <t>1,92; 16,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 18,85</t>
+          <t>2,12; 18,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,55</t>
+          <t>0,0; 16,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,15</t>
+          <t>7,09; 23,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 34,39</t>
+          <t>14,77; 34,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 21,56</t>
+          <t>4,33; 20,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 25,71</t>
+          <t>9,01; 26,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,58</t>
+          <t>7,46; 18,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 24,23</t>
+          <t>10,97; 24,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,76</t>
+          <t>4,98; 16,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 19,85</t>
+          <t>7,46; 20,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,32</t>
+          <t>9,32; 17,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 23,23</t>
+          <t>8,43; 22,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,19; 25,58</t>
+          <t>10,3; 25,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 26,85</t>
+          <t>12,53; 26,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,98; 23,56</t>
+          <t>11,81; 22,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,05; 28,98</t>
+          <t>15,02; 28,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 25,33</t>
+          <t>13,45; 25,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 23,58</t>
+          <t>10,15; 22,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 23,89</t>
+          <t>16,49; 24,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,63</t>
+          <t>13,86; 24,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 22,98</t>
+          <t>13,79; 23,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 21,61</t>
+          <t>12,33; 21,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 22,33</t>
+          <t>16,06; 22,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,0</t>
+          <t>7,1; 17,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 20,67</t>
+          <t>8,83; 20,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,43</t>
+          <t>9,13; 21,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 21,02</t>
+          <t>11,83; 20,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,59</t>
+          <t>16,56; 27,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 21,98</t>
+          <t>12,38; 21,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 22,14</t>
+          <t>11,5; 21,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 21,65</t>
+          <t>15,5; 21,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,25</t>
+          <t>14,77; 22,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,9</t>
+          <t>11,98; 19,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,38</t>
+          <t>11,91; 19,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 20,15</t>
+          <t>15,13; 20,27</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>17735</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>795; 7210</t>
+          <t>803; 6945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1010; 8567</t>
+          <t>963; 8570</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5187</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3451; 11673</t>
+          <t>3907; 12959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10109; 23267</t>
+          <t>9992; 23090</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3591; 15029</t>
+          <t>3018; 14582</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7982; 21115</t>
+          <t>7399; 21690</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5979; 14303</t>
+          <t>6005; 15005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11856; 26515</t>
+          <t>12003; 27101</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5381; 18146</t>
+          <t>5739; 19189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8333; 22521</t>
+          <t>8466; 23261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11072; 22619</t>
+          <t>12635; 24188</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50442</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>74837</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7295; 19699</t>
+          <t>7148; 19438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10264; 25758</t>
+          <t>10373; 25692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10703; 24194</t>
+          <t>11291; 24243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12774; 25128</t>
+          <t>13465; 26201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24564; 47308</t>
+          <t>24520; 46868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27704; 53136</t>
+          <t>28226; 52608</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19246; 43679</t>
+          <t>18800; 42470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42017; 60960</t>
+          <t>45631; 66793</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34931; 61087</t>
+          <t>34390; 60813</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44023; 71369</t>
+          <t>42825; 73706</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32667; 59489</t>
+          <t>33945; 59804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57756; 80822</t>
+          <t>62759; 87313</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>92571</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8978; 22788</t>
+          <t>8993; 22591</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12907; 30208</t>
+          <t>12905; 30593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11444; 26023</t>
+          <t>11091; 25643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18667; 33011</t>
+          <t>20002; 35469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38499; 63705</t>
+          <t>38243; 63953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34794; 61431</t>
+          <t>34608; 60147</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30705; 59190</t>
+          <t>30741; 57077</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50322; 71059</t>
+          <t>55390; 77733</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52046; 79541</t>
+          <t>52795; 80466</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53131; 84693</t>
+          <t>50978; 83270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45469; 75345</t>
+          <t>46327; 76812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74166; 97772</t>
+          <t>79630; 106687</t>
         </is>
       </c>
     </row>
